--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA4F838D-BA74-4335-9944-37353DD64D9A}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09DD6249-28CD-457E-92CC-63CBE9AC3038}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
   <si>
     <t>Symbol</t>
   </si>
@@ -65,67 +65,46 @@
     <t>sell</t>
   </si>
   <si>
-    <t>buy</t>
-  </si>
-  <si>
-    <t>BSE</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>JKTYRE</t>
-  </si>
-  <si>
-    <t>INE573A01042</t>
-  </si>
-  <si>
-    <t>BEL</t>
-  </si>
-  <si>
-    <t>INE263A01024</t>
-  </si>
-  <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>81200</t>
-  </si>
-  <si>
-    <t>1772422200326002151</t>
-  </si>
-  <si>
-    <t>2026-03-02T09:00:08</t>
-  </si>
-  <si>
-    <t>2026-03-06</t>
-  </si>
-  <si>
-    <t>12056500</t>
-  </si>
-  <si>
-    <t>1772786628145883616</t>
-  </si>
-  <si>
-    <t>2026-03-06T15:06:07</t>
-  </si>
-  <si>
-    <t>MRPL</t>
-  </si>
-  <si>
-    <t>INE103A01014</t>
-  </si>
-  <si>
-    <t>408247693</t>
-  </si>
-  <si>
-    <t>1200000077068736</t>
-  </si>
-  <si>
-    <t>2026-03-06T15:29:10</t>
-  </si>
-  <si>
-    <t>408247694</t>
+    <t>SUPREMEIND</t>
+  </si>
+  <si>
+    <t>INE195A01028</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
+    <t>602393096</t>
+  </si>
+  <si>
+    <t>1300000019368715</t>
+  </si>
+  <si>
+    <t>2025-10-03T10:12:04</t>
+  </si>
+  <si>
+    <t>602393097</t>
+  </si>
+  <si>
+    <t>602393094</t>
+  </si>
+  <si>
+    <t>CIPLA</t>
+  </si>
+  <si>
+    <t>INE059A01026</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>4407184</t>
+  </si>
+  <si>
+    <t>1000000050030745</t>
+  </si>
+  <si>
+    <t>2026-02-02T12:08:58</t>
   </si>
 </sst>
 </file>
@@ -167,12 +146,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -191,10 +169,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -506,167 +480,167 @@
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2">
+        <v>4180.2002000000002</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="M2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>196</v>
-      </c>
-      <c r="K2" s="3">
-        <v>420.4</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>26</v>
+      <c r="N2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4180.2002000000002</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" t="s">
         <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>54</v>
-      </c>
-      <c r="K3" s="3">
-        <v>468.3</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="b">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
         <v>0</v>
       </c>
-      <c r="J4" s="3">
-        <v>42</v>
-      </c>
-      <c r="K4" s="3">
-        <v>206.6</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>35</v>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>4180.2002000000002</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>1299.4000000000001</v>
+      </c>
+      <c r="L5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <v>79</v>
-      </c>
-      <c r="K5" s="3">
-        <v>206.6</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>35</v>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09DD6249-28CD-457E-92CC-63CBE9AC3038}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80C27D1C-5407-44A0-B7CA-4BD62B337677}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Symbol</t>
   </si>
@@ -62,49 +62,28 @@
     <t>EQ</t>
   </si>
   <si>
+    <t>PIDILITIND</t>
+  </si>
+  <si>
+    <t>INE318A01026</t>
+  </si>
+  <si>
+    <t>2025-10-03</t>
+  </si>
+  <si>
     <t>sell</t>
   </si>
   <si>
-    <t>SUPREMEIND</t>
-  </si>
-  <si>
-    <t>INE195A01028</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>602393096</t>
-  </si>
-  <si>
-    <t>1300000019368715</t>
-  </si>
-  <si>
-    <t>2025-10-03T10:12:04</t>
-  </si>
-  <si>
-    <t>602393097</t>
-  </si>
-  <si>
-    <t>602393094</t>
-  </si>
-  <si>
-    <t>CIPLA</t>
-  </si>
-  <si>
-    <t>INE059A01026</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
-    <t>4407184</t>
-  </si>
-  <si>
-    <t>1000000050030745</t>
-  </si>
-  <si>
-    <t>2026-02-02T12:08:58</t>
+    <t>402016993</t>
+  </si>
+  <si>
+    <t>1200000018561473</t>
+  </si>
+  <si>
+    <t>2025-10-03T10:12:36</t>
+  </si>
+  <si>
+    <t>402016995</t>
   </si>
 </sst>
 </file>
@@ -169,6 +148,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N5"/>
+  <dimension ref="B1:N3"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -481,13 +464,13 @@
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>13</v>
@@ -499,16 +482,16 @@
         <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2" s="2">
-        <v>4180.2002000000002</v>
+        <v>1477.1</v>
       </c>
       <c r="L2" t="s">
         <v>19</v>
@@ -522,13 +505,13 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -540,16 +523,16 @@
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K3" s="2">
-        <v>4180.2002000000002</v>
+        <v>1477.1</v>
       </c>
       <c r="L3" t="s">
         <v>22</v>
@@ -559,88 +542,6 @@
       </c>
       <c r="N3" t="s">
         <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1</v>
-      </c>
-      <c r="K4" s="2">
-        <v>4180.2002000000002</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>1</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1299.4000000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>27</v>
-      </c>
-      <c r="M5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,19 +3,35 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80C27D1C-5407-44A0-B7CA-4BD62B337677}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACFC4E3E-9093-49C5-AD6C-C9DF2DEA75B7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equity" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Symbol</t>
   </si>
@@ -54,36 +70,6 @@
   </si>
   <si>
     <t>Order Execution Time</t>
-  </si>
-  <si>
-    <t>NSE</t>
-  </si>
-  <si>
-    <t>EQ</t>
-  </si>
-  <si>
-    <t>PIDILITIND</t>
-  </si>
-  <si>
-    <t>INE318A01026</t>
-  </si>
-  <si>
-    <t>2025-10-03</t>
-  </si>
-  <si>
-    <t>sell</t>
-  </si>
-  <si>
-    <t>402016993</t>
-  </si>
-  <si>
-    <t>1200000018561473</t>
-  </si>
-  <si>
-    <t>2025-10-03T10:12:36</t>
-  </si>
-  <si>
-    <t>402016995</t>
   </si>
 </sst>
 </file>
@@ -125,12 +111,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -148,10 +131,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -412,7 +391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N3"/>
+  <dimension ref="B1:N1"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -462,88 +441,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>4</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1477.1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="2">
-        <v>4</v>
-      </c>
-      <c r="K3" s="2">
-        <v>1477.1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" t="s">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACFC4E3E-9093-49C5-AD6C-C9DF2DEA75B7}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10943619-6E3A-4340-B3F1-AE20634377C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equity" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
   <si>
     <t>Symbol</t>
   </si>
@@ -70,13 +70,46 @@
   </si>
   <si>
     <t>Order Execution Time</t>
+  </si>
+  <si>
+    <t>BANKBARODA</t>
+  </si>
+  <si>
+    <t>INE028A01039</t>
+  </si>
+  <si>
+    <t>2026-02-02</t>
+  </si>
+  <si>
+    <t>NSE</t>
+  </si>
+  <si>
+    <t>EQ</t>
+  </si>
+  <si>
+    <t>sell</t>
+  </si>
+  <si>
+    <t>1000000039324729</t>
+  </si>
+  <si>
+    <t>2026-02-02T11:20:59</t>
+  </si>
+  <si>
+    <t>3556965</t>
+  </si>
+  <si>
+    <t>3556967</t>
+  </si>
+  <si>
+    <t>3556966</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +120,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -111,11 +150,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -131,6 +174,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -391,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N1"/>
+  <dimension ref="B1:N4"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -441,6 +488,129 @@
         <v>12</v>
       </c>
     </row>
+    <row r="2" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2">
+        <v>271.55</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2">
+        <v>271.55</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>70</v>
+      </c>
+      <c r="K4" s="2">
+        <v>271.55</v>
+      </c>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="38" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10943619-6E3A-4340-B3F1-AE20634377C5}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{752980CE-3DC3-4B77-B4D9-CD4EAEF702D0}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>Symbol</t>
   </si>
@@ -72,44 +72,41 @@
     <t>Order Execution Time</t>
   </si>
   <si>
-    <t>BANKBARODA</t>
-  </si>
-  <si>
-    <t>INE028A01039</t>
-  </si>
-  <si>
-    <t>2026-02-02</t>
-  </si>
-  <si>
     <t>NSE</t>
   </si>
   <si>
     <t>EQ</t>
   </si>
   <si>
-    <t>sell</t>
-  </si>
-  <si>
-    <t>1000000039324729</t>
-  </si>
-  <si>
-    <t>2026-02-02T11:20:59</t>
-  </si>
-  <si>
-    <t>3556965</t>
-  </si>
-  <si>
-    <t>3556967</t>
-  </si>
-  <si>
-    <t>3556966</t>
+    <t>TATATECH</t>
+  </si>
+  <si>
+    <t>INE142M01025</t>
+  </si>
+  <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>buy</t>
+  </si>
+  <si>
+    <t>610264981</t>
+  </si>
+  <si>
+    <t>1300000103548770</t>
+  </si>
+  <si>
+    <t>2026-05-19T15:18:13</t>
+  </si>
+  <si>
+    <t>610264982</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,12 +117,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -155,10 +146,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N4"/>
+  <dimension ref="B1:N3"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -489,126 +480,85 @@
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2">
-        <v>10</v>
-      </c>
-      <c r="K2" s="2">
-        <v>271.55</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="K2" s="3">
+        <v>670.55</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="3" t="b">
+      <c r="I3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="2">
-        <v>10</v>
-      </c>
-      <c r="K3" s="2">
-        <v>271.55</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="J3" s="3">
+        <v>59</v>
+      </c>
+      <c r="K3" s="3">
+        <v>670.55</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="M3" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2">
-        <v>70</v>
-      </c>
-      <c r="K4" s="2">
-        <v>271.55</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>20</v>
+      <c r="N3" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="40" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{752980CE-3DC3-4B77-B4D9-CD4EAEF702D0}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC3D52E7-A341-4753-B129-046335400DB4}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Symbol</t>
   </si>
@@ -78,28 +78,25 @@
     <t>EQ</t>
   </si>
   <si>
-    <t>TATATECH</t>
-  </si>
-  <si>
-    <t>INE142M01025</t>
-  </si>
-  <si>
-    <t>2026-05-19</t>
-  </si>
-  <si>
     <t>buy</t>
   </si>
   <si>
-    <t>610264981</t>
-  </si>
-  <si>
-    <t>1300000103548770</t>
-  </si>
-  <si>
-    <t>2026-05-19T15:18:13</t>
-  </si>
-  <si>
-    <t>610264982</t>
+    <t>CUPID</t>
+  </si>
+  <si>
+    <t>INE509F01029</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2098313</t>
+  </si>
+  <si>
+    <t>1000000020034216</t>
+  </si>
+  <si>
+    <t>2026-05-26T10:12:23</t>
   </si>
 </sst>
 </file>
@@ -141,9 +138,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -165,10 +165,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -429,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N3"/>
+  <dimension ref="B1:N12"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -480,86 +476,85 @@
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2" t="b">
+      <c r="I2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="J2" s="3">
-        <v>16</v>
-      </c>
-      <c r="K2" s="3">
-        <v>670.55</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="J2" s="4">
+        <v>389</v>
+      </c>
+      <c r="K2" s="4">
+        <v>128.84</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>59</v>
-      </c>
-      <c r="K3" s="3">
-        <v>670.55</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>21</v>
-      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="45" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC3D52E7-A341-4753-B129-046335400DB4}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C7B02D4-D7C9-494F-A558-4D8098FB8636}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Equity" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -81,22 +81,142 @@
     <t>buy</t>
   </si>
   <si>
-    <t>CUPID</t>
-  </si>
-  <si>
-    <t>INE509F01029</t>
-  </si>
-  <si>
-    <t>2026-05-26</t>
-  </si>
-  <si>
-    <t>2098313</t>
-  </si>
-  <si>
-    <t>1000000020034216</t>
-  </si>
-  <si>
-    <t>2026-05-26T10:12:23</t>
+    <t>THERMAX</t>
+  </si>
+  <si>
+    <t>INE152A01029</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>608407266</t>
+  </si>
+  <si>
+    <t>1300000084210335</t>
+  </si>
+  <si>
+    <t>2026-06-01T14:06:20</t>
+  </si>
+  <si>
+    <t>SKIPPER</t>
+  </si>
+  <si>
+    <t>INE439E01022</t>
+  </si>
+  <si>
+    <t>608423928</t>
+  </si>
+  <si>
+    <t>1300000084371531</t>
+  </si>
+  <si>
+    <t>2026-06-01T14:07:05</t>
+  </si>
+  <si>
+    <t>608423927</t>
+  </si>
+  <si>
+    <t>NETWEB</t>
+  </si>
+  <si>
+    <t>INE0NT901020</t>
+  </si>
+  <si>
+    <t>407166647</t>
+  </si>
+  <si>
+    <t>1200000080958672</t>
+  </si>
+  <si>
+    <t>2026-06-01T14:08:17</t>
+  </si>
+  <si>
+    <t>407166649</t>
+  </si>
+  <si>
+    <t>407166648</t>
+  </si>
+  <si>
+    <t>ZYDUSLIFE</t>
+  </si>
+  <si>
+    <t>INE010B01027</t>
+  </si>
+  <si>
+    <t>608538891</t>
+  </si>
+  <si>
+    <t>1300000085516858</t>
+  </si>
+  <si>
+    <t>2026-06-01T14:12:10</t>
+  </si>
+  <si>
+    <t>608538892</t>
+  </si>
+  <si>
+    <t>TRITURBINE</t>
+  </si>
+  <si>
+    <t>INE152M01016</t>
+  </si>
+  <si>
+    <t>608626693</t>
+  </si>
+  <si>
+    <t>1300000086413096</t>
+  </si>
+  <si>
+    <t>2026-06-01T14:15:44</t>
+  </si>
+  <si>
+    <t>608626692</t>
+  </si>
+  <si>
+    <t>608626694</t>
+  </si>
+  <si>
+    <t>608626695</t>
+  </si>
+  <si>
+    <t>608626696</t>
+  </si>
+  <si>
+    <t>EXIDEIND</t>
+  </si>
+  <si>
+    <t>INE302A01020</t>
+  </si>
+  <si>
+    <t>208620145</t>
+  </si>
+  <si>
+    <t>1100000080505821</t>
+  </si>
+  <si>
+    <t>2026-06-01T14:17:15</t>
+  </si>
+  <si>
+    <t>208620146</t>
+  </si>
+  <si>
+    <t>208620144</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>610983964</t>
+  </si>
+  <si>
+    <t>1300000098406459</t>
+  </si>
+  <si>
+    <t>2026-05-29T15:16:11</t>
+  </si>
+  <si>
+    <t>610983965</t>
   </si>
 </sst>
 </file>
@@ -138,15 +258,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -165,6 +281,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -425,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:N12"/>
+  <dimension ref="B1:N19"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -476,85 +596,742 @@
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>389</v>
-      </c>
-      <c r="K2" s="4">
-        <v>128.84</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2">
+        <v>4</v>
+      </c>
+      <c r="K2" s="2">
+        <v>4949.7997999999998</v>
+      </c>
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="2">
+        <v>4</v>
+      </c>
+      <c r="K3" s="2">
+        <v>4949.7997999999998</v>
+      </c>
+      <c r="L3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3</v>
+      </c>
+      <c r="K4" s="2">
+        <v>4997.3999000000003</v>
+      </c>
+      <c r="L4" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M4" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-    </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>15</v>
+      </c>
+      <c r="K5" s="2">
+        <v>547</v>
+      </c>
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>77</v>
+      </c>
+      <c r="K6" s="2">
+        <v>547</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" s="2">
+        <v>4599</v>
+      </c>
+      <c r="L7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>4599.2002000000002</v>
+      </c>
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>5</v>
+      </c>
+      <c r="K9" s="2">
+        <v>4599.1000999999997</v>
+      </c>
+      <c r="L9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" t="s">
+        <v>31</v>
+      </c>
+      <c r="N9" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2">
+        <v>11</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1092.4000000000001</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" t="s">
+        <v>38</v>
+      </c>
+      <c r="N10" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2">
+        <v>35</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1092.4000000000001</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="B12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
+        <v>697.1</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s">
+        <v>44</v>
+      </c>
+      <c r="N12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2">
+        <v>22</v>
+      </c>
+      <c r="K13" s="2">
+        <v>697.1</v>
+      </c>
+      <c r="L13" t="s">
+        <v>46</v>
+      </c>
+      <c r="M13" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2">
+        <v>3</v>
+      </c>
+      <c r="K14" s="2">
+        <v>697.1</v>
+      </c>
+      <c r="L14" t="s">
+        <v>47</v>
+      </c>
+      <c r="M14" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2">
+        <v>37</v>
+      </c>
+      <c r="K15" s="2">
+        <v>697.1</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" t="s">
+        <v>44</v>
+      </c>
+      <c r="N15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2">
+        <v>9</v>
+      </c>
+      <c r="K16" s="2">
+        <v>697.1</v>
+      </c>
+      <c r="L16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M16" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2">
+        <v>111</v>
+      </c>
+      <c r="K17" s="2">
+        <v>389.65</v>
+      </c>
+      <c r="L17" t="s">
+        <v>52</v>
+      </c>
+      <c r="M17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2">
+        <v>13</v>
+      </c>
+      <c r="K18" s="2">
+        <v>389.65</v>
+      </c>
+      <c r="L18" t="s">
+        <v>55</v>
+      </c>
+      <c r="M18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2">
+        <v>5</v>
+      </c>
+      <c r="K19" s="2">
+        <v>389.65</v>
+      </c>
+      <c r="L19" t="s">
+        <v>56</v>
+      </c>
+      <c r="M19" t="s">
+        <v>53</v>
+      </c>
+      <c r="N19" t="s">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tradebook Template.xlsx
+++ b/Tradebook Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46D75A32-2695-4048-88FC-00D86510DD5B}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="11_B8E6E54BA230E35AD1C0AFADF073B256A24125FE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6348F31-F2B5-4DB8-9065-716907BEEF85}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -81,70 +81,184 @@
     <t>buy</t>
   </si>
   <si>
-    <t>SOLARINDS</t>
-  </si>
-  <si>
-    <t>INE343H01029</t>
-  </si>
-  <si>
-    <t>TDPOWERSYS</t>
-  </si>
-  <si>
-    <t>INE419M01027</t>
-  </si>
-  <si>
-    <t>GVT&amp;D</t>
-  </si>
-  <si>
-    <t>INE200A01026</t>
-  </si>
-  <si>
-    <t>2026-06-04T11:45:35</t>
-  </si>
-  <si>
     <t>BSE</t>
   </si>
   <si>
     <t>A</t>
   </si>
   <si>
-    <t>2026-06-04T11:48:33</t>
-  </si>
-  <si>
-    <t>2026-06-04T11:55:25</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>205454282</t>
-  </si>
-  <si>
-    <t>1100000050186797</t>
-  </si>
-  <si>
-    <t>5961700</t>
-  </si>
-  <si>
-    <t>1780550482158604643</t>
-  </si>
-  <si>
-    <t>5962300</t>
-  </si>
-  <si>
-    <t>5962100</t>
-  </si>
-  <si>
-    <t>5961900</t>
-  </si>
-  <si>
-    <t>5962500</t>
-  </si>
-  <si>
-    <t>604868027</t>
-  </si>
-  <si>
-    <t>1300000047270644</t>
+    <t>SUNPHARMA</t>
+  </si>
+  <si>
+    <t>INE044A01036</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>sell</t>
+  </si>
+  <si>
+    <t>607608623</t>
+  </si>
+  <si>
+    <t>1300000080435508</t>
+  </si>
+  <si>
+    <t>2026-06-05T14:11:19</t>
+  </si>
+  <si>
+    <t>607608625</t>
+  </si>
+  <si>
+    <t>607608624</t>
+  </si>
+  <si>
+    <t>GPIL</t>
+  </si>
+  <si>
+    <t>INE177H01039</t>
+  </si>
+  <si>
+    <t>207863043</t>
+  </si>
+  <si>
+    <t>1100000081623474</t>
+  </si>
+  <si>
+    <t>2026-06-05T14:11:52</t>
+  </si>
+  <si>
+    <t>207863041</t>
+  </si>
+  <si>
+    <t>207863052</t>
+  </si>
+  <si>
+    <t>207863050</t>
+  </si>
+  <si>
+    <t>207863046</t>
+  </si>
+  <si>
+    <t>207863042</t>
+  </si>
+  <si>
+    <t>207863051</t>
+  </si>
+  <si>
+    <t>207863049</t>
+  </si>
+  <si>
+    <t>207863047</t>
+  </si>
+  <si>
+    <t>207863048</t>
+  </si>
+  <si>
+    <t>207863045</t>
+  </si>
+  <si>
+    <t>207863044</t>
+  </si>
+  <si>
+    <t>TATATECH</t>
+  </si>
+  <si>
+    <t>INE142M01025</t>
+  </si>
+  <si>
+    <t>8566100</t>
+  </si>
+  <si>
+    <t>1780650791219152130</t>
+  </si>
+  <si>
+    <t>2026-06-05T14:54:16</t>
+  </si>
+  <si>
+    <t>LAURUSLABS</t>
+  </si>
+  <si>
+    <t>INE947Q01028</t>
+  </si>
+  <si>
+    <t>6439100</t>
+  </si>
+  <si>
+    <t>1780646107540983562</t>
+  </si>
+  <si>
+    <t>2026-06-05T14:55:18</t>
+  </si>
+  <si>
+    <t>BALAMINES</t>
+  </si>
+  <si>
+    <t>INE050E01027</t>
+  </si>
+  <si>
+    <t>6653160</t>
+  </si>
+  <si>
+    <t>1000000077505165</t>
+  </si>
+  <si>
+    <t>2026-06-05T14:58:19</t>
+  </si>
+  <si>
+    <t>6653157</t>
+  </si>
+  <si>
+    <t>6653161</t>
+  </si>
+  <si>
+    <t>6653158</t>
+  </si>
+  <si>
+    <t>6653159</t>
+  </si>
+  <si>
+    <t>7090800</t>
+  </si>
+  <si>
+    <t>1780651635390503732</t>
+  </si>
+  <si>
+    <t>2026-06-05T15:21:19</t>
+  </si>
+  <si>
+    <t>ZENTEC</t>
+  </si>
+  <si>
+    <t>INE251B01027</t>
+  </si>
+  <si>
+    <t>609856815</t>
+  </si>
+  <si>
+    <t>1300000099844907</t>
+  </si>
+  <si>
+    <t>2026-06-05T15:24:23</t>
+  </si>
+  <si>
+    <t>609856816</t>
+  </si>
+  <si>
+    <t>EXIDEIND</t>
+  </si>
+  <si>
+    <t>INE302A01020</t>
+  </si>
+  <si>
+    <t>210316684</t>
+  </si>
+  <si>
+    <t>1100000100822022</t>
+  </si>
+  <si>
+    <t>2026-06-05T15:27:06</t>
   </si>
 </sst>
 </file>
@@ -531,43 +645,43 @@
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="I2" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J2" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K2" s="4">
-        <v>5100</v>
+        <v>1790.5</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
@@ -578,37 +692,37 @@
         <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4">
+        <v>1790.3</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>18</v>
-      </c>
-      <c r="K3" s="4">
-        <v>1350.75</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.25">
@@ -619,296 +733,999 @@
         <v>19</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>15</v>
+      </c>
+      <c r="K4" s="4">
+        <v>1790.3</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>3</v>
-      </c>
-      <c r="K4" s="4">
-        <v>1351</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I5" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J5" s="4">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="K5" s="4">
-        <v>1350.85</v>
+        <v>280.75</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I6" s="3" t="b">
         <v>0</v>
       </c>
       <c r="J6" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K6" s="4">
-        <v>1350.8</v>
+        <v>280.75</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="M6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4">
         <v>19</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4">
-        <v>5</v>
-      </c>
       <c r="K7" s="4">
-        <v>1351.1</v>
+        <v>280.64999999999998</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N7" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <v>30</v>
+      </c>
+      <c r="K8" s="4">
+        <v>280.64999999999998</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>30</v>
+      </c>
+      <c r="K9" s="4">
+        <v>280.7</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <v>30</v>
+      </c>
+      <c r="K10" s="4">
+        <v>280.75</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <v>32</v>
+      </c>
+      <c r="K11" s="4">
+        <v>280.64999999999998</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>88</v>
+      </c>
+      <c r="K12" s="4">
+        <v>280.7</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>9</v>
+      </c>
+      <c r="K13" s="4">
+        <v>280.7</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <v>9</v>
+      </c>
+      <c r="K14" s="4">
+        <v>280.7</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4">
+        <v>10</v>
+      </c>
+      <c r="K15" s="4">
+        <v>280.75</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>9</v>
+      </c>
+      <c r="K16" s="4">
+        <v>280.75</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="F17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4">
-        <v>2</v>
-      </c>
-      <c r="K8" s="4">
-        <v>18502</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="10:11" x14ac:dyDescent="0.25">
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="I17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4">
+        <v>65</v>
+      </c>
+      <c r="K17" s="4">
+        <v>767.25</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>34</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1449.5</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>11</v>
+      </c>
+      <c r="K19" s="4">
+        <v>2027.9</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4">
+        <v>1</v>
+      </c>
+      <c r="K20" s="4">
+        <v>2027.6</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <v>29</v>
+      </c>
+      <c r="K21" s="4">
+        <v>2028</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <v>4</v>
+      </c>
+      <c r="K22" s="4">
+        <v>2027.6</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="4">
+        <v>4</v>
+      </c>
+      <c r="K23" s="4">
+        <v>2027.8</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <v>34</v>
+      </c>
+      <c r="K24" s="4">
+        <v>1446.35</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4">
+        <v>5</v>
+      </c>
+      <c r="K25" s="4">
+        <v>1817.3</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4">
+        <v>9</v>
+      </c>
+      <c r="K26" s="4">
+        <v>1817.8</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4">
+        <v>125</v>
+      </c>
+      <c r="K27" s="4">
+        <v>399.6</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="10:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
